--- a/data/trans_dic/P20-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P20-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,36</t>
+          <t>3,28; 7,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,57</t>
+          <t>2,86; 7,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,79</t>
+          <t>3,95; 8,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,17</t>
+          <t>4,49; 8,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,35</t>
+          <t>3,84; 9,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 14,93</t>
+          <t>7,63; 15,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,33</t>
+          <t>6,95; 13,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,29</t>
+          <t>5,25; 9,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,23</t>
+          <t>4,1; 7,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,76</t>
+          <t>5,49; 9,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,96</t>
+          <t>5,79; 9,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,41</t>
+          <t>5,12; 8,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,88</t>
+          <t>2,39; 6,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,59</t>
+          <t>2,38; 6,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,18</t>
+          <t>3,34; 8,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,17</t>
+          <t>3,05; 6,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,31</t>
+          <t>5,24; 10,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,61</t>
+          <t>7,1; 13,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,74</t>
+          <t>6,31; 12,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,05</t>
+          <t>5,49; 10,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,96</t>
+          <t>4,43; 7,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,61</t>
+          <t>4,7; 8,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,48</t>
+          <t>5,38; 9,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,58</t>
+          <t>4,74; 7,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,63</t>
+          <t>2,52; 5,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,33</t>
+          <t>5,91; 10,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,51</t>
+          <t>4,34; 8,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,32</t>
+          <t>1,61; 8,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 15,7</t>
+          <t>5,62; 15,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 12,49</t>
+          <t>5,56; 12,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 15,54</t>
+          <t>5,39; 15,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 15,52</t>
+          <t>6,17; 15,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,25</t>
+          <t>3,72; 7,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,14</t>
+          <t>6,47; 10,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,24</t>
+          <t>5,06; 9,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,66</t>
+          <t>2,39; 8,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,82</t>
+          <t>3,46; 5,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,96</t>
+          <t>5,06; 8,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,12</t>
+          <t>3,47; 6,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,54</t>
+          <t>4,45; 7,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,07</t>
+          <t>6,77; 11,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 12,97</t>
+          <t>8,48; 13,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 11,24</t>
+          <t>7,48; 11,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,46</t>
+          <t>2,76; 7,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,23</t>
+          <t>5,0; 7,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,39</t>
+          <t>6,79; 9,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,72</t>
+          <t>5,66; 7,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,76</t>
+          <t>3,99; 6,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,02</t>
+          <t>2,53; 6,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,1</t>
+          <t>5,16; 10,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,17</t>
+          <t>2,13; 5,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,99</t>
+          <t>6,22; 10,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,59</t>
+          <t>5,16; 9,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,97</t>
+          <t>8,37; 12,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,51</t>
+          <t>4,66; 8,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,67</t>
+          <t>3,49; 6,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,81</t>
+          <t>4,6; 7,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,98</t>
+          <t>7,66; 11,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,35</t>
+          <t>4,06; 6,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,57</t>
+          <t>4,86; 7,53</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,66</t>
+          <t>0,3; 3,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,28</t>
+          <t>1,46; 5,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,7</t>
+          <t>1,5; 5,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,61</t>
+          <t>0,29; 5,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,0</t>
+          <t>5,23; 7,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,31</t>
+          <t>6,21; 9,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,88</t>
+          <t>4,74; 7,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,05</t>
+          <t>4,12; 7,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,77</t>
+          <t>4,38; 6,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,22</t>
+          <t>5,47; 8,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,03</t>
+          <t>4,28; 6,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,79</t>
+          <t>3,26; 5,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,9</t>
+          <t>3,49; 4,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,85</t>
+          <t>5,2; 6,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,58</t>
+          <t>4,14; 5,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,44</t>
+          <t>4,32; 6,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,4</t>
+          <t>6,52; 8,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,56</t>
+          <t>8,54; 10,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,67</t>
+          <t>6,84; 8,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,7</t>
+          <t>4,78; 6,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,41</t>
+          <t>5,24; 6,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,48</t>
+          <t>7,17; 8,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,95</t>
+          <t>5,69; 6,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,42</t>
+          <t>4,92; 6,39</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15679; 34892</t>
+          <t>15547; 34047</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13126; 33108</t>
+          <t>12502; 33903</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17086; 37724</t>
+          <t>16929; 38277</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22505; 46342</t>
+          <t>22690; 44047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12209; 28690</t>
+          <t>11769; 27831</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24020; 46934</t>
+          <t>24008; 48666</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23911; 46268</t>
+          <t>24125; 47453</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22266; 41567</t>
+          <t>23491; 42287</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31262; 56451</t>
+          <t>32020; 57121</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41408; 73356</t>
+          <t>41258; 72513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45027; 77337</t>
+          <t>44941; 76229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50028; 80165</t>
+          <t>48746; 78135</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8859; 25255</t>
+          <t>8766; 24651</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10843; 27583</t>
+          <t>9984; 27292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12492; 30861</t>
+          <t>12586; 32849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14502; 32412</t>
+          <t>13789; 31092</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20141; 42041</t>
+          <t>19471; 40552</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22739; 46011</t>
+          <t>23994; 46420</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24620; 47434</t>
+          <t>23502; 46480</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20651; 38466</t>
+          <t>21016; 39602</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31957; 58835</t>
+          <t>32739; 58820</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37901; 65193</t>
+          <t>35576; 65295</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41859; 71071</t>
+          <t>40350; 70302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38706; 63280</t>
+          <t>39558; 64804</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13106; 30558</t>
+          <t>13668; 31782</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36358; 65043</t>
+          <t>37176; 65051</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22380; 44420</t>
+          <t>22645; 44709</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11687; 55618</t>
+          <t>10743; 53715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10208; 26348</t>
+          <t>9433; 26576</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14677; 32493</t>
+          <t>14466; 33632</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8703; 25809</t>
+          <t>8955; 25165</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9978; 25904</t>
+          <t>10300; 25595</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26732; 51501</t>
+          <t>26414; 53808</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56008; 90231</t>
+          <t>57559; 90655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35753; 63597</t>
+          <t>34799; 62666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17623; 72322</t>
+          <t>19933; 71733</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43604; 72050</t>
+          <t>42849; 72748</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58938; 92285</t>
+          <t>58632; 93021</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41293; 70323</t>
+          <t>39868; 69830</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46111; 78029</t>
+          <t>46022; 78019</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48558; 79076</t>
+          <t>48362; 79060</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64367; 99431</t>
+          <t>64994; 100463</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59658; 92833</t>
+          <t>61806; 96285</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27701; 73005</t>
+          <t>26970; 71956</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101164; 141182</t>
+          <t>97654; 140621</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132347; 180846</t>
+          <t>130800; 182425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108806; 152489</t>
+          <t>111857; 155437</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79380; 136065</t>
+          <t>80391; 136731</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9452; 24594</t>
+          <t>8876; 24032</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25993; 51556</t>
+          <t>26334; 52365</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13444; 32118</t>
+          <t>13212; 33103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29671; 52194</t>
+          <t>29531; 50647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28909; 54545</t>
+          <t>29335; 56093</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64049; 98742</t>
+          <t>63729; 97547</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34807; 62810</t>
+          <t>34423; 61548</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29744; 55920</t>
+          <t>29254; 54206</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42648; 71809</t>
+          <t>42258; 71022</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96939; 139655</t>
+          <t>97394; 142826</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53444; 86232</t>
+          <t>55119; 87428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62545; 99409</t>
+          <t>63893; 98923</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>888; 10885</t>
+          <t>886; 10972</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3789; 13985</t>
+          <t>3864; 14701</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4701; 16355</t>
+          <t>4308; 16154</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>568; 8688</t>
+          <t>691; 12443</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63479; 99869</t>
+          <t>65271; 96849</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69535; 103268</t>
+          <t>68878; 104384</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50506; 85256</t>
+          <t>51244; 84902</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31274; 53676</t>
+          <t>31356; 56087</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68197; 104676</t>
+          <t>67686; 102047</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76468; 112899</t>
+          <t>75221; 112471</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58228; 96249</t>
+          <t>58578; 94318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33080; 58007</t>
+          <t>32659; 57066</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114730; 160050</t>
+          <t>114153; 159715</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>178552; 234158</t>
+          <t>177766; 234085</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>138505; 188784</t>
+          <t>140190; 190791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144461; 217286</t>
+          <t>145822; 218520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>221383; 283697</t>
+          <t>220282; 283130</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>299847; 374841</t>
+          <t>303343; 373186</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>242521; 306227</t>
+          <t>241709; 308340</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>169874; 239486</t>
+          <t>171054; 241519</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>349964; 425773</t>
+          <t>348385; 421616</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>495234; 590830</t>
+          <t>499601; 592751</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>395495; 480553</t>
+          <t>393869; 478221</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>343434; 446374</t>
+          <t>341985; 443982</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P20-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,19</t>
+          <t>3,13; 7,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,75</t>
+          <t>3,05; 7,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,92</t>
+          <t>3,98; 8,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,72</t>
+          <t>4,13; 8,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,07</t>
+          <t>3,77; 9,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 15,48</t>
+          <t>7,78; 15,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 13,67</t>
+          <t>6,7; 13,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,45</t>
+          <t>5,32; 10,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,32</t>
+          <t>4,04; 7,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,65</t>
+          <t>5,48; 9,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,82</t>
+          <t>5,72; 9,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,2</t>
+          <t>5,34; 8,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,72</t>
+          <t>2,31; 6,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,52</t>
+          <t>2,42; 6,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,71</t>
+          <t>3,15; 8,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,88</t>
+          <t>3,2; 6,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,91</t>
+          <t>5,4; 11,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 13,73</t>
+          <t>6,97; 13,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,49</t>
+          <t>6,52; 12,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,35</t>
+          <t>5,86; 10,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,96</t>
+          <t>4,56; 7,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,63</t>
+          <t>4,91; 8,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,38</t>
+          <t>5,61; 9,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,76</t>
+          <t>4,97; 7,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,86</t>
+          <t>2,47; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,34</t>
+          <t>5,63; 10,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,57</t>
+          <t>4,28; 8,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,04</t>
+          <t>5,56; 10,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,84</t>
+          <t>5,6; 14,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,93</t>
+          <t>5,69; 12,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,15</t>
+          <t>5,22; 15,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,33</t>
+          <t>6,05; 15,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,58</t>
+          <t>3,76; 7,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,19</t>
+          <t>6,38; 10,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,11</t>
+          <t>5,08; 9,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,59</t>
+          <t>6,37; 10,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,87</t>
+          <t>3,46; 5,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,03</t>
+          <t>5,02; 7,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,07</t>
+          <t>3,65; 6,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,54</t>
+          <t>4,23; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 11,07</t>
+          <t>6,94; 11,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,48; 13,1</t>
+          <t>8,64; 13,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,66</t>
+          <t>7,32; 11,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,36</t>
+          <t>5,52; 8,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,2</t>
+          <t>5,19; 7,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,47</t>
+          <t>6,78; 9,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,87</t>
+          <t>5,54; 7,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,79</t>
+          <t>5,22; 7,3</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,86</t>
+          <t>2,41; 6,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,26</t>
+          <t>5,32; 9,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,33</t>
+          <t>2,11; 5,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,66</t>
+          <t>5,81; 10,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,86</t>
+          <t>5,11; 9,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,81</t>
+          <t>8,28; 12,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,34</t>
+          <t>4,62; 8,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,46</t>
+          <t>4,27; 7,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,73</t>
+          <t>4,63; 7,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,23</t>
+          <t>7,62; 11,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,43</t>
+          <t>3,93; 6,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,53</t>
+          <t>5,35; 7,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,69</t>
+          <t>0,3; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,55</t>
+          <t>1,46; 5,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,63</t>
+          <t>1,63; 5,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,17</t>
+          <t>0,58; 5,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,76</t>
+          <t>5,25; 7,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,41</t>
+          <t>6,23; 9,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,85</t>
+          <t>4,58; 7,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,37</t>
+          <t>3,99; 6,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,6</t>
+          <t>4,33; 6,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,18</t>
+          <t>5,38; 8,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,89</t>
+          <t>4,26; 6,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,7</t>
+          <t>3,41; 6,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,89</t>
+          <t>3,46; 4,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 6,84</t>
+          <t>5,25; 7,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 5,64</t>
+          <t>4,13; 5,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,47</t>
+          <t>5,23; 6,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,38</t>
+          <t>6,48; 8,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,51</t>
+          <t>8,43; 10,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,73</t>
+          <t>6,9; 8,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,75</t>
+          <t>5,86; 7,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,34</t>
+          <t>5,21; 6,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,5</t>
+          <t>7,2; 8,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,91</t>
+          <t>5,74; 6,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,39</t>
+          <t>5,69; 6,8</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>69097</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15547; 34047</t>
+          <t>14837; 34794</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12502; 33903</t>
+          <t>13335; 33552</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16929; 38277</t>
+          <t>17070; 37680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22690; 44047</t>
+          <t>22721; 44838</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11769; 27831</t>
+          <t>11550; 28609</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24008; 48666</t>
+          <t>24452; 47354</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24125; 47453</t>
+          <t>23238; 46284</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23491; 42287</t>
+          <t>25998; 49082</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32020; 57121</t>
+          <t>31506; 56831</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41258; 72513</t>
+          <t>41176; 72936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44941; 76229</t>
+          <t>44369; 77332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48746; 78135</t>
+          <t>55528; 86305</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>56683</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8766; 24651</t>
+          <t>8465; 24475</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9984; 27292</t>
+          <t>10131; 28389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12586; 32849</t>
+          <t>11881; 30691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13789; 31092</t>
+          <t>15465; 33739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19471; 40552</t>
+          <t>20082; 41956</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23994; 46420</t>
+          <t>23543; 45766</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23502; 46480</t>
+          <t>24281; 47732</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21016; 39602</t>
+          <t>24799; 44534</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32739; 58820</t>
+          <t>33724; 58463</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35576; 65295</t>
+          <t>37167; 67078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40350; 70302</t>
+          <t>42061; 71334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39558; 64804</t>
+          <t>45039; 70507</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>55285</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13668; 31782</t>
+          <t>13377; 30958</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37176; 65051</t>
+          <t>35424; 65139</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22645; 44709</t>
+          <t>22345; 44309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10743; 53715</t>
+          <t>26243; 49563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9433; 26576</t>
+          <t>9392; 25052</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14466; 33632</t>
+          <t>14793; 32650</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8955; 25165</t>
+          <t>8669; 26493</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10300; 25595</t>
+          <t>11349; 29550</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26414; 53808</t>
+          <t>26733; 51052</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57559; 90655</t>
+          <t>56765; 91171</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34799; 62666</t>
+          <t>34984; 63657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19933; 71733</t>
+          <t>41988; 69617</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>112243</t>
+          <t>122767</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42849; 72748</t>
+          <t>42819; 73739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58632; 93021</t>
+          <t>58177; 91087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39868; 69830</t>
+          <t>41968; 71941</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46022; 78019</t>
+          <t>47876; 79528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48362; 79060</t>
+          <t>49568; 79610</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64994; 100463</t>
+          <t>66201; 101557</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61806; 96285</t>
+          <t>60475; 95616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26970; 71956</t>
+          <t>47536; 74098</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97654; 140621</t>
+          <t>101275; 142176</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130800; 182425</t>
+          <t>130565; 178931</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111857; 155437</t>
+          <t>109506; 153942</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80391; 136731</t>
+          <t>103999; 145554</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>90895</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8876; 24032</t>
+          <t>8453; 23850</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26334; 52365</t>
+          <t>27172; 50223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13212; 33103</t>
+          <t>13068; 32365</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29531; 50647</t>
+          <t>32996; 57964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29335; 56093</t>
+          <t>29082; 55932</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63729; 97547</t>
+          <t>63089; 97855</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34423; 61548</t>
+          <t>34085; 61062</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29254; 54206</t>
+          <t>35440; 62039</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42258; 71022</t>
+          <t>42575; 72000</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97394; 142826</t>
+          <t>96996; 141710</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55119; 87428</t>
+          <t>53407; 87543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63893; 98923</t>
+          <t>74733; 111450</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>48051</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>886; 10972</t>
+          <t>888; 10723</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3864; 14701</t>
+          <t>3865; 14465</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4308; 16154</t>
+          <t>4681; 17163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>691; 12443</t>
+          <t>1370; 12157</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65271; 96849</t>
+          <t>65531; 99693</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68878; 104384</t>
+          <t>69165; 104491</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51244; 84902</t>
+          <t>49521; 83401</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31356; 56087</t>
+          <t>33662; 58149</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67686; 102047</t>
+          <t>66991; 102750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75221; 112471</t>
+          <t>73886; 112304</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58578; 94318</t>
+          <t>58273; 94212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32659; 57066</t>
+          <t>36902; 64941</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>204382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>210439</t>
+          <t>238396</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>397785</t>
+          <t>442777</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114153; 159715</t>
+          <t>113052; 159036</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>177766; 234085</t>
+          <t>179642; 239247</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>140190; 190791</t>
+          <t>139962; 188700</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145822; 218520</t>
+          <t>180072; 234732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>220282; 283130</t>
+          <t>218751; 280389</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>303343; 373186</t>
+          <t>299161; 372945</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>241709; 308340</t>
+          <t>243753; 311786</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>171054; 241519</t>
+          <t>212922; 266850</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>348385; 421616</t>
+          <t>346364; 420427</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>499601; 592751</t>
+          <t>502007; 595394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>393869; 478221</t>
+          <t>397377; 482872</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>341985; 443982</t>
+          <t>402717; 480931</t>
         </is>
       </c>
     </row>
